--- a/data/trans_dic/AIRE_1_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/AIRE_1_R-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>83,16; 90,68</t>
+          <t>82,86; 90,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>87,26; 92,29</t>
+          <t>87,3; 92,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86,54; 90,84</t>
+          <t>86,84; 91,03</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>70,82; 77,46</t>
+          <t>71,12; 77,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>70,57; 86,26</t>
+          <t>70,18; 86,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71,91; 81,9</t>
+          <t>72,01; 82,32</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54,41; 66,31</t>
+          <t>53,81; 66,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62,31; 71,07</t>
+          <t>62,34; 71,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59,84; 67,56</t>
+          <t>60,02; 66,98</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>71,08; 75,92</t>
+          <t>70,79; 76,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>73,39; 84,37</t>
+          <t>73,36; 84,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73,44; 79,82</t>
+          <t>73,22; 80,42</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>212282; 231471</t>
+          <t>211516; 231312</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>332637; 351810</t>
+          <t>332803; 351673</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>550809; 578161</t>
+          <t>552718; 579412</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>761390; 832746</t>
+          <t>764648; 832546</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>848303; 1036849</t>
+          <t>843569; 1036567</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1637570; 1865030</t>
+          <t>1639704; 1874468</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>176181; 214707</t>
+          <t>174240; 214232</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>201053; 229295</t>
+          <t>201123; 230016</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>386819; 436775</t>
+          <t>387977; 432988</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1175781; 1255903</t>
+          <t>1170933; 1258137</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1398745; 1608013</t>
+          <t>1398105; 1612956</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2614408; 2841450</t>
+          <t>2606508; 2862811</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/AIRE_1_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/AIRE_1_R-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,04%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>82,86; 90,62</t>
+          <t>83,23; 91,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>87,3; 92,25</t>
+          <t>87,4; 92,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86,84; 91,03</t>
+          <t>86,74; 91,03</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>74,93%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>71,12; 77,44</t>
+          <t>72,11; 77,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>70,18; 86,24</t>
+          <t>72,3; 77,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72,01; 82,32</t>
+          <t>72,81; 76,74</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,12%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>53,81; 66,16</t>
+          <t>52,83; 63,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62,34; 71,29</t>
+          <t>62,96; 71,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60,02; 66,98</t>
+          <t>59,61; 66,68</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,38%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>70,79; 76,06</t>
+          <t>71,56; 76,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>73,36; 84,63</t>
+          <t>75,01; 78,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73,22; 80,42</t>
+          <t>73,97; 76,72</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>223266</t>
+          <t>255798</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>343313</t>
+          <t>376937</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>566579</t>
+          <t>632734</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>211516; 231312</t>
+          <t>243177; 266210</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>332803; 351673</t>
+          <t>365730; 386642</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>552718; 579412</t>
+          <t>616354; 646835</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>799568</t>
+          <t>871069</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>924661</t>
+          <t>801798</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1724229</t>
+          <t>1672868</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>764648; 832546</t>
+          <t>836619; 904256</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>843569; 1036567</t>
+          <t>775254; 825941</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1639704; 1874468</t>
+          <t>1625604; 1713236</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>194245</t>
+          <t>202378</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>215692</t>
+          <t>245962</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>409938</t>
+          <t>448340</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>174240; 214232</t>
+          <t>183139; 220626</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>201123; 230016</t>
+          <t>228942; 260130</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>387977; 432988</t>
+          <t>423404; 473603</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1217080</t>
+          <t>1329244</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1483665</t>
+          <t>1424698</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2700745</t>
+          <t>2753942</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1170933; 1258137</t>
+          <t>1287482; 1369098</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1398105; 1612956</t>
+          <t>1390901; 1454035</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2606508; 2862811</t>
+          <t>2702323; 2802951</t>
         </is>
       </c>
     </row>
